--- a/output/Data and Chart Outputs/united_kingdom_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/united_kingdom_power_capacity_monthly.xlsx
@@ -169,7 +169,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>UK installed capacity, month-end: solar (DESNZ ET 6.3), wind, bioenergy, storage (REPD rebuild) (to Jun/26)</a:t>
+              <a:t>UK installed capacity, month-end: solar (DESNZ ET 6.3), others (REPD rebuild) (to Jun/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -8939,10 +8939,10 @@
         <v>14115.41</v>
       </c>
       <c r="E2" t="n">
-        <v>-532.5600000000013</v>
+        <v>-532.5599999999995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9622710215289531</v>
+        <v>0.9622710215289532</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -9065,10 +9065,10 @@
         <v>14211.71</v>
       </c>
       <c r="E7" t="n">
-        <v>-579.1600000000017</v>
+        <v>-579.1599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.959247690812717</v>
+        <v>0.9592476908127171</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>14075.26</v>
       </c>
       <c r="E9" t="n">
-        <v>35.45700000000215</v>
+        <v>35.45700000000033</v>
       </c>
       <c r="F9" t="n">
         <v>1.002519100890499</v>
@@ -9218,10 +9218,10 @@
         <v>11066.88</v>
       </c>
       <c r="E13" t="n">
-        <v>-639.380000000001</v>
+        <v>-639.3799999999992</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9422258125144575</v>
+        <v>0.9422258125144576</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>14150.35</v>
       </c>
       <c r="E14" t="n">
-        <v>39.04399999999805</v>
+        <v>39.04399999999987</v>
       </c>
       <c r="F14" t="n">
         <v>1.002759225036836</v>
@@ -9317,10 +9317,10 @@
         <v>14492.75</v>
       </c>
       <c r="E17" t="n">
-        <v>-731.1000000000022</v>
+        <v>-731.1000000000004</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9495540873885217</v>
+        <v>0.9495540873885219</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -9443,10 +9443,10 @@
         <v>14632.81</v>
       </c>
       <c r="E22" t="n">
-        <v>-787.659999999998</v>
+        <v>-787.6599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.946171651241286</v>
+        <v>0.9461716512412859</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>14178.81</v>
       </c>
       <c r="E24" t="n">
-        <v>267.1979999999985</v>
+        <v>267.1980000000003</v>
       </c>
       <c r="F24" t="n">
         <v>1.018844881904758</v>
@@ -9749,7 +9749,7 @@
         <v>14564.97</v>
       </c>
       <c r="E34" t="n">
-        <v>255.3339999999989</v>
+        <v>255.3340000000007</v>
       </c>
       <c r="F34" t="n">
         <v>1.017530691789959</v>
@@ -9821,10 +9821,10 @@
         <v>14840.36</v>
       </c>
       <c r="E37" t="n">
-        <v>-995.2099999999991</v>
+        <v>-995.2100000000009</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9329389583541101</v>
+        <v>0.9329389583541099</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -9875,10 +9875,10 @@
         <v>14812.56</v>
       </c>
       <c r="E39" t="n">
-        <v>326.9159999999993</v>
+        <v>326.9160000000011</v>
       </c>
       <c r="F39" t="n">
-        <v>1.022070189082778</v>
+        <v>1.022070189082779</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -9974,10 +9974,10 @@
         <v>14734.68</v>
       </c>
       <c r="E43" t="n">
-        <v>-1130.679999999998</v>
+        <v>-1130.68</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9232640274508847</v>
+        <v>0.9232640274508845</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -10073,10 +10073,10 @@
         <v>15445.29</v>
       </c>
       <c r="E47" t="n">
-        <v>-1070.939999999999</v>
+        <v>-1070.940000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9306623572623112</v>
+        <v>0.9306623572623111</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -10100,10 +10100,10 @@
         <v>14734.68</v>
       </c>
       <c r="E48" t="n">
-        <v>-1130.679999999998</v>
+        <v>-1130.68</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9232640274508847</v>
+        <v>0.9232640274508845</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -10226,10 +10226,10 @@
         <v>14734.68</v>
       </c>
       <c r="E53" t="n">
-        <v>-1130.679999999998</v>
+        <v>-1130.68</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9232640274508847</v>
+        <v>0.9232640274508845</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -10352,10 +10352,10 @@
         <v>14734.68</v>
       </c>
       <c r="E58" t="n">
-        <v>-55.67999999999847</v>
+        <v>-55.68000000000029</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9962211598758848</v>
+        <v>0.9962211598758847</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -10478,10 +10478,10 @@
         <v>14809.68</v>
       </c>
       <c r="E63" t="n">
-        <v>-130.6799999999985</v>
+        <v>-130.6800000000003</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9911760416160242</v>
+        <v>0.9911760416160241</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -10577,10 +10577,10 @@
         <v>15655.36</v>
       </c>
       <c r="E67" t="n">
-        <v>-1157.509999999998</v>
+        <v>-1157.51</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9260630225047525</v>
+        <v>0.9260630225047524</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10604,10 +10604,10 @@
         <v>15691.68</v>
       </c>
       <c r="E68" t="n">
-        <v>-1012.679999999998</v>
+        <v>-1012.68</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9354638891438012</v>
+        <v>0.9354638891438011</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10730,10 +10730,10 @@
         <v>15691.68</v>
       </c>
       <c r="E73" t="n">
-        <v>-1012.679999999998</v>
+        <v>-1012.68</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9354638891438012</v>
+        <v>0.9354638891438011</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -10829,10 +10829,10 @@
         <v>16199.27</v>
       </c>
       <c r="E77" t="n">
-        <v>-1084.219999999999</v>
+        <v>-1084.220000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>0.9330698235167387</v>
+        <v>0.9330698235167386</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -10856,10 +10856,10 @@
         <v>16139.68</v>
       </c>
       <c r="E78" t="n">
-        <v>-1460.679999999998</v>
+        <v>-1460.68</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9094975860735778</v>
+        <v>0.9094975860735777</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -10955,10 +10955,10 @@
         <v>16154.27</v>
       </c>
       <c r="E82" t="n">
-        <v>-1030.019999999999</v>
+        <v>-1030.02</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9362385301223763</v>
+        <v>0.9362385301223762</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>16314.68</v>
       </c>
       <c r="E83" t="n">
-        <v>-1635.679999999998</v>
+        <v>-1635.68</v>
       </c>
       <c r="F83" t="n">
         <v>0.8997418276055675</v>
@@ -11009,7 +11009,7 @@
         <v>19908.37</v>
       </c>
       <c r="E84" t="n">
-        <v>176.9709999999977</v>
+        <v>176.9710000000014</v>
       </c>
       <c r="F84" t="n">
         <v>1.008889276218997</v>
@@ -11081,10 +11081,10 @@
         <v>16316.28</v>
       </c>
       <c r="E87" t="n">
-        <v>-1091.23</v>
+        <v>-1091.230000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>0.9331201719999902</v>
+        <v>0.9331201719999901</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>20371.15</v>
       </c>
       <c r="E89" t="n">
-        <v>178.6110000000008</v>
+        <v>178.6109999999971</v>
       </c>
       <c r="F89" t="n">
         <v>1.008767840794457</v>
@@ -11387,7 +11387,7 @@
         <v>21914.97</v>
       </c>
       <c r="E99" t="n">
-        <v>168.5450000000019</v>
+        <v>168.5449999999983</v>
       </c>
       <c r="F99" t="n">
         <v>1.007690861543502</v>
@@ -11513,7 +11513,7 @@
         <v>22215.12</v>
       </c>
       <c r="E104" t="n">
-        <v>242.3119999999981</v>
+        <v>242.3120000000017</v>
       </c>
       <c r="F104" t="n">
         <v>1.010907526045324</v>
@@ -11639,7 +11639,7 @@
         <v>22427.34</v>
       </c>
       <c r="E109" t="n">
-        <v>550.3290000000052</v>
+        <v>550.3290000000015</v>
       </c>
       <c r="F109" t="n">
         <v>1.024538309046013</v>
@@ -11752,7 +11752,7 @@
         <v>14492.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1710999999977503</v>
+        <v>0.1710999999995693</v>
       </c>
     </row>
     <row r="3">
@@ -11974,7 +11974,7 @@
         <v>14840.36</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01500000000123691</v>
+        <v>0.01499999999941792</v>
       </c>
     </row>
     <row r="15">
@@ -12012,7 +12012,7 @@
         <v>14812.56</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4098000000012689</v>
+        <v>-0.4097999999994499</v>
       </c>
     </row>
     <row r="17">
@@ -12215,7 +12215,7 @@
         <v>14734.68</v>
       </c>
       <c r="E27" t="n">
-        <v>0.195000000001528</v>
+        <v>0.194999999999709</v>
       </c>
     </row>
     <row r="28">
@@ -12253,7 +12253,7 @@
         <v>1895.85</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05109999999990578</v>
+        <v>0.05110000000013315</v>
       </c>
     </row>
     <row r="30">
@@ -12418,7 +12418,7 @@
         <v>16199.27</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1911999999992986</v>
+        <v>-0.1912000000011176</v>
       </c>
     </row>
     <row r="39">
@@ -12437,7 +12437,7 @@
         <v>16139.68</v>
       </c>
       <c r="E39" t="n">
-        <v>0.195000000001528</v>
+        <v>0.194999999999709</v>
       </c>
     </row>
     <row r="40">
@@ -12475,7 +12475,7 @@
         <v>1895.85</v>
       </c>
       <c r="E41" t="n">
-        <v>0.05109999999990578</v>
+        <v>0.05110000000013315</v>
       </c>
     </row>
     <row r="42">
@@ -12678,7 +12678,7 @@
         <v>21914.97</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.03269999999611173</v>
+        <v>-0.03269999999974971</v>
       </c>
     </row>
     <row r="53">
@@ -12697,7 +12697,7 @@
         <v>1895.85</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2489000000000487</v>
+        <v>-0.2488999999998214</v>
       </c>
     </row>
     <row r="54">
@@ -12913,10 +12913,8 @@
           <t>Mon, 28 Sep 2026 13:57:33 GMT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>477750</t>
-        </is>
+      <c r="D2" t="n">
+        <v>477750</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -12945,10 +12943,8 @@
           <t>Mon, 28 Sep 2026 13:58:50 GMT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>880636</t>
-        </is>
+      <c r="D3" t="n">
+        <v>880636</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -12977,10 +12973,8 @@
           <t>Fri, 31 Jul 2026 15:22:40 GMT</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5087389</t>
-        </is>
+      <c r="D4" t="n">
+        <v>5087389</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13014,10 +13008,8 @@
           <t>Wed, 29 Jul 2026 17:20:40 GMT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
+      <c r="D5" t="n">
+        <v>50514</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13046,10 +13038,8 @@
           <t>Wed, 29 Jul 2026 17:21:36 GMT</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>44708</t>
-        </is>
+      <c r="D6" t="n">
+        <v>44708</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
